--- a/site_date.xlsx
+++ b/site_date.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katar\OneDrive - nevada.unr.edu\NEON\Abv-Workspace-09202023_laptop\Summarizing-Input-Data\Finalizing Code on 10102023\Site by Site\Monte-Carlo\MC-Matlab-Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katar\Documents\PhD\Chapter 1\Response to Reviewers\Consolidating Final Versions\Public Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C3042C-D058-4233-AEB9-92B655EF2422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA2B7E8-B58C-41B5-9F5C-0BD02F13D740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="495" windowWidth="25515" windowHeight="13875" xr2:uid="{B1D617A1-3374-4E95-BE0C-A02D3272FBF2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B1D617A1-3374-4E95-BE0C-A02D3272FBF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,41 +57,20 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -100,12 +79,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,9 +418,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF7F159-8CAB-4683-B3B2-E64D97D8C87E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.78515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.78515625" style="2" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,31 +432,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B2" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B3" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B4" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>2020</v>
       </c>
@@ -483,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>2020</v>
       </c>
@@ -491,7 +472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>2020</v>
       </c>
@@ -499,7 +480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>2021</v>
       </c>
@@ -507,7 +488,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>2021</v>
       </c>
@@ -515,7 +496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>2021</v>
       </c>
@@ -523,39 +504,39 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B11" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B12" s="2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B13" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B14" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B13" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>2020</v>
       </c>
@@ -563,7 +544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>2020</v>
       </c>
@@ -571,31 +552,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B17" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B18" s="2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B17" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B18" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B19" s="2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B19" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>2020</v>
       </c>
@@ -603,7 +584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2020</v>
       </c>
@@ -611,7 +592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -619,7 +600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
@@ -627,7 +608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>2021</v>
       </c>
@@ -635,7 +616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2021</v>
       </c>
@@ -643,23 +624,23 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B26" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B27" s="2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B26" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B27" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>2021</v>
       </c>
@@ -667,7 +648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>2021</v>
       </c>
@@ -675,7 +656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2021</v>
       </c>
@@ -683,7 +664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>2021</v>
       </c>
@@ -691,47 +672,47 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B32" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B33" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B34" s="2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B32" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B33" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B34" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B35" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B36" s="2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B35" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B36" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2020</v>
       </c>
@@ -739,7 +720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>2020</v>
       </c>
@@ -747,7 +728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>2021</v>
       </c>
@@ -755,7 +736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>2021</v>
       </c>
@@ -763,7 +744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>2021</v>
       </c>
@@ -771,31 +752,31 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B42" s="2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B42" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B43" s="2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B43" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B44" s="2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B44" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>2020</v>
       </c>
@@ -803,7 +784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>2020</v>
       </c>
@@ -811,7 +792,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>2021</v>
       </c>
@@ -819,83 +800,83 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="1">
         <v>2019</v>
       </c>
-      <c r="B48" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+      <c r="B48" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="1">
         <v>2019</v>
       </c>
-      <c r="B49" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+      <c r="B49" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="1">
         <v>2019</v>
       </c>
-      <c r="B50" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+      <c r="B50" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" s="1">
         <v>2019</v>
       </c>
-      <c r="B51" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+      <c r="B51" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" s="1">
         <v>2019</v>
       </c>
-      <c r="B52" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B53" s="2">
+      <c r="B52" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B53" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B54" s="2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B54" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B55" s="2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B55" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B56" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B57" s="2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A56" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B56" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A57" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B57" s="1">
         <v>7</v>
       </c>
     </row>
